--- a/sources/table_normalization/xlsx/economy-table12.xlsx
+++ b/sources/table_normalization/xlsx/economy-table12.xlsx
@@ -349,7 +349,6 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -370,13 +369,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -385,7 +382,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal 2" xfId="3"/>
@@ -881,11 +881,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="D1" s="23">
+      <c r="D1" s="22">
         <v>3</v>
       </c>
     </row>
@@ -894,80 +894,80 @@
       <c r="B2" s="6"/>
     </row>
     <row r="3" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7"/>
     </row>
     <row r="4" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="27" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="28" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="30" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:21" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="34"/>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="35"/>
+      <c r="E13" s="37"/>
       <c r="F13" s="33" t="s">
         <v>17</v>
       </c>
@@ -976,18 +976,18 @@
         <v>18</v>
       </c>
       <c r="I13" s="34"/>
-      <c r="J13" s="35" t="s">
+      <c r="J13" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="35"/>
+      <c r="K13" s="37"/>
       <c r="L13" s="33" t="s">
         <v>20</v>
       </c>
       <c r="M13" s="34"/>
-      <c r="N13" s="36" t="s">
+      <c r="N13" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="O13" s="37"/>
+      <c r="O13" s="36"/>
       <c r="P13" s="33" t="s">
         <v>22</v>
       </c>
@@ -1002,7 +1002,7 @@
       <c r="U13" s="34"/>
     </row>
     <row r="14" spans="1:21" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -1088,16 +1088,16 @@
       <c r="G15" s="13">
         <v>24020715.761693999</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>815804.98128645495</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="19">
         <v>930127.73558018997</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="20">
         <v>3272904.8837580602</v>
       </c>
-      <c r="K15" s="21">
+      <c r="K15" s="20">
         <v>4349956.5209671604</v>
       </c>
       <c r="L15" s="12">
@@ -1118,7 +1118,7 @@
       <c r="Q15" s="13">
         <v>2775419.5555765601</v>
       </c>
-      <c r="R15" s="19">
+      <c r="R15" s="18">
         <v>2086978.9113889299</v>
       </c>
       <c r="S15" s="13">
@@ -1153,16 +1153,16 @@
       <c r="G16" s="13">
         <v>17287.066669588501</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="18">
         <v>1553.6704983388499</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="19">
         <v>2833.1299887</v>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="20">
         <v>3711.10236195173</v>
       </c>
-      <c r="K16" s="21">
+      <c r="K16" s="20">
         <v>2326.00287750895</v>
       </c>
       <c r="L16" s="12">
@@ -1183,7 +1183,7 @@
       <c r="Q16" s="13">
         <v>7949.4442966446504</v>
       </c>
-      <c r="R16" s="19">
+      <c r="R16" s="18">
         <v>6845.1282801790503</v>
       </c>
       <c r="S16" s="13">
@@ -1218,16 +1218,16 @@
       <c r="G17" s="13">
         <v>67347.789870320106</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="18">
         <v>7374.0745146672498</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="19">
         <v>9596.8212344583008</v>
       </c>
-      <c r="J17" s="21">
+      <c r="J17" s="20">
         <v>22062.461169308601</v>
       </c>
-      <c r="K17" s="21">
+      <c r="K17" s="20">
         <v>10869.696973497001</v>
       </c>
       <c r="L17" s="12">
@@ -1248,7 +1248,7 @@
       <c r="Q17" s="13">
         <v>29683.639745471399</v>
       </c>
-      <c r="R17" s="19">
+      <c r="R17" s="18">
         <v>20535.384840537201</v>
       </c>
       <c r="S17" s="13">
@@ -1283,16 +1283,16 @@
       <c r="G18" s="13">
         <v>1398080.0875772201</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="18">
         <v>240293.055975383</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="19">
         <v>239400.10405049101</v>
       </c>
-      <c r="J18" s="21">
+      <c r="J18" s="20">
         <v>708197.97765843198</v>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="20">
         <v>760919.30134496395</v>
       </c>
       <c r="L18" s="12">
@@ -1313,7 +1313,7 @@
       <c r="Q18" s="13">
         <v>400853.05967044801</v>
       </c>
-      <c r="R18" s="19">
+      <c r="R18" s="18">
         <v>355184.61766296503</v>
       </c>
       <c r="S18" s="13">
@@ -1334,102 +1334,102 @@
       <c r="E19" s="14"/>
       <c r="F19" s="12"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
       <c r="L19" s="12"/>
       <c r="M19" s="13"/>
       <c r="N19" s="12"/>
       <c r="O19" s="13"/>
       <c r="P19" s="12"/>
       <c r="Q19" s="13"/>
-      <c r="R19" s="19"/>
+      <c r="R19" s="18"/>
       <c r="S19" s="13"/>
       <c r="T19" s="12"/>
       <c r="U19" s="13"/>
     </row>
     <row r="20" spans="1:23" ht="13" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="16">
         <f t="shared" ref="B20:U20" si="0">SUM(B15:B18)</f>
         <v>1844041.0427453299</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="17">
         <f t="shared" si="0"/>
         <v>2329007.4882863802</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="16">
         <f t="shared" si="0"/>
         <v>3830712.7321298998</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <f t="shared" si="0"/>
         <v>3889277.6459324299</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="16">
         <f t="shared" si="0"/>
         <v>23239431.273682099</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="17">
         <f t="shared" si="0"/>
         <v>25503430.705811098</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="16">
         <f t="shared" si="0"/>
         <v>1065025.7822748399</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="17">
         <f t="shared" si="0"/>
         <v>1181957.7908538401</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="16">
         <f t="shared" si="0"/>
         <v>4006876.4249477498</v>
       </c>
-      <c r="K20" s="18">
+      <c r="K20" s="17">
         <f t="shared" si="0"/>
         <v>5124071.5221631303</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="16">
         <f t="shared" si="0"/>
         <v>12150428.932719801</v>
       </c>
-      <c r="M20" s="18">
+      <c r="M20" s="17">
         <f t="shared" si="0"/>
         <v>12167931.6824264</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="16">
         <f t="shared" si="0"/>
         <v>2785110.2071868698</v>
       </c>
-      <c r="O20" s="18">
+      <c r="O20" s="17">
         <f t="shared" si="0"/>
         <v>2943580.2645152002</v>
       </c>
-      <c r="P20" s="17">
+      <c r="P20" s="16">
         <f t="shared" si="0"/>
         <v>3023322.9668926899</v>
       </c>
-      <c r="Q20" s="18">
+      <c r="Q20" s="17">
         <f t="shared" si="0"/>
         <v>3213905.6992891198</v>
       </c>
-      <c r="R20" s="17">
+      <c r="R20" s="16">
         <f t="shared" si="0"/>
         <v>2469544.0421726098</v>
       </c>
-      <c r="S20" s="18">
+      <c r="S20" s="17">
         <f t="shared" si="0"/>
         <v>2576756.0048425398</v>
       </c>
-      <c r="T20" s="17">
+      <c r="T20" s="16">
         <f t="shared" si="0"/>
         <v>54474812.7539078</v>
       </c>
-      <c r="U20" s="18">
+      <c r="U20" s="17">
         <f t="shared" si="0"/>
         <v>59662156.670522898</v>
       </c>
@@ -2061,16 +2061,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
     <mergeCell ref="L13:M13"/>
     <mergeCell ref="N13:O13"/>
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="R13:S13"/>
     <mergeCell ref="T13:U13"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
